--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50431-2024 artfynd.xlsx
+++ b/artfynd/A 50431-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933000</v>
       </c>
       <c r="B2" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933001</v>
       </c>
       <c r="B3" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
